--- a/docs/pin_list.xlsx
+++ b/docs/pin_list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5b2da16fa1785921/MyDocuments/Community/ISHIKAI/shuttle/OpenSUSI-TR10/2026/ExtraDesign/OpenSUSI-TR1um-v2609_05/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="466" documentId="11_AD4D066CA252ABDACC1048686197E6B673EEDF5D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D5835121-BD23-46F9-BE33-305BFA500CB0}"/>
+  <xr:revisionPtr revIDLastSave="473" documentId="11_AD4D066CA252ABDACC1048686197E6B673EEDF5D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7DC446C-F4C3-4C9C-9A32-D88E56DDB4E5}"/>
   <bookViews>
     <workbookView xWindow="38330" yWindow="0" windowWidth="19200" windowHeight="9980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="20">
   <si>
     <t>Pin Number</t>
     <phoneticPr fontId="1"/>
@@ -54,6 +54,10 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>G</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>IN_AMP</t>
   </si>
   <si>
@@ -81,6 +85,26 @@
   </si>
   <si>
     <t>RGB121_VGA</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>HSYNC</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VSYNC</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>CLK</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -505,10 +529,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="18.350000000000001" thickBot="1">
@@ -516,10 +540,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="18.350000000000001" thickTop="1">
@@ -527,10 +551,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -538,10 +562,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -549,27 +573,33 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="2"/>
+        <v>14</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="7" spans="1:3" ht="18.350000000000001" thickBot="1">
       <c r="A7" s="5">
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="6"/>
+        <v>13</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="8" spans="1:3" ht="18.350000000000001" thickTop="1">
       <c r="A8" s="3">
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="4"/>
+        <v>13</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="1">
@@ -587,46 +617,54 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="2"/>
+        <v>13</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="11" spans="1:3" ht="18.350000000000001" thickBot="1">
       <c r="A11" s="5">
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="6"/>
+        <v>13</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="12" spans="1:3" ht="18.350000000000001" thickTop="1">
       <c r="A12" s="8">
         <v>11</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="9"/>
+        <v>13</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="1">
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" s="2"/>
+        <v>13</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="1">
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="18.350000000000001" thickBot="1">
@@ -634,10 +672,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="18.350000000000001" thickTop="1">
@@ -645,10 +683,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="18.350000000000001" thickBot="1">
@@ -749,6 +787,6 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="87" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>